--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
+++ b/branches/release-3.0.0/ValueSet-be-vs-radiology-supporting-info-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
